--- a/4-CPM_index/cultural_production_index_database.xlsx
+++ b/4-CPM_index/cultural_production_index_database.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -584,172 +584,160 @@
       <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Variable</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>macro_region_name</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Broad geographic grouping (e.g., Western Europe, Asia)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>macro_region</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Broad geographic grouping (e.g., Western Europe, Asia)</t>
+          <t>Geographic region (modern country or historical region)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>decade</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Geographic region (modern country or historical region)</t>
+          <t>Amount of cultural production for one decade</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>decade</t>
+          <t>n_cultural_producers</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Decade of activity</t>
+          <t>Number of observed cultural producers in the data</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>n_cultural_producers</t>
+          <t>cultural_production</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Number of observed cultural producers in the data</t>
+          <t>Unseen species model estimate of cultural producers (point estimate)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>cultural_production</t>
+          <t>cultural_production_min</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Unseen species model estimate of cultural producers (point estimate)</t>
+          <t>Lower bound of the 94% credible interval</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>cultural_production_min</t>
+          <t>cultural_production_max</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Lower bound of the 94% credible interval</t>
+          <t>Upper bound of the 94% credible interval</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>cultural_production_max</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Upper bound of the 94% credible interval</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC COVERAGE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>GEOGRAPHIC COVERAGE</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>The database covers the following macro-regions:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>The database covers the following macro-regions:</t>
+          <t>- Ancient Mediterranean</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>- Ancient Mediterranean</t>
+          <t>- Asia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>- Asia</t>
+          <t>- Eastern Europe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>- Eastern Europe</t>
+          <t>- Middle-East and Africa (MENA)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>- Middle-East and Africa (MENA)</t>
+          <t>- Western Europe</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>- Western Europe</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TEMPORAL COVERAGE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>TEMPORAL COVERAGE</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>From: -820 to 1880</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>From: -820 to 1880</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Unit: Decades</t>
         </is>
@@ -778,7 +766,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>macro_region</t>
+          <t>macro_region_name</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -788,7 +776,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>countries</t>
+          <t>modern_countries</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -1351,7 +1339,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>macro_region</t>
+          <t>macro_region_name</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
